--- a/data.xlsx
+++ b/data.xlsx
@@ -5,44 +5,44 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ys.chun\Desktop\8. 징계\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ys.chun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC57421-39B4-4D6D-82F9-BF55D27D5120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D5D98E-A5C6-46D0-8367-5C782D423DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="징계기록대장_2018" sheetId="1" r:id="rId1"/>
-    <sheet name="징계기록대장_2019" sheetId="2" r:id="rId2"/>
-    <sheet name="징계기록대장_2020" sheetId="3" r:id="rId3"/>
-    <sheet name="징계기록대장_2021" sheetId="5" r:id="rId4"/>
-    <sheet name="징계기록대장_2022" sheetId="6" r:id="rId5"/>
-    <sheet name="징계기록대장_2023" sheetId="7" r:id="rId6"/>
-    <sheet name="징계기록대장_2024" sheetId="8" r:id="rId7"/>
-    <sheet name="징계기록대장_2025" sheetId="9" r:id="rId8"/>
-    <sheet name="집계표(2018_2026)" sheetId="4" r:id="rId9"/>
+    <sheet name="2018년" sheetId="1" r:id="rId1"/>
+    <sheet name="2019년" sheetId="2" r:id="rId2"/>
+    <sheet name="2020년" sheetId="3" r:id="rId3"/>
+    <sheet name="2021년" sheetId="5" r:id="rId4"/>
+    <sheet name="2022년" sheetId="6" r:id="rId5"/>
+    <sheet name="2023년" sheetId="7" r:id="rId6"/>
+    <sheet name="2024년" sheetId="8" r:id="rId7"/>
+    <sheet name="2025년" sheetId="9" r:id="rId8"/>
+    <sheet name="2026년" sheetId="4" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'집계표(2018_2026)'!$A$7:$J$126</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'집계표(2018_2026)'!$A$1:$J$125</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">징계기록대장_2018!$A$1:$K$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">징계기록대장_2019!$A$1:$K$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">징계기록대장_2020!$A$1:$K$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">징계기록대장_2021!$A$1:$K$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">징계기록대장_2022!$A$1:$K$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">징계기록대장_2023!$A$1:$J$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">징계기록대장_2024!$A$1:$J$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">징계기록대장_2025!$A$1:$J$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'집계표(2018_2026)'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">징계기록대장_2018!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">징계기록대장_2019!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">징계기록대장_2020!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">징계기록대장_2021!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">징계기록대장_2022!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">징계기록대장_2023!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">징계기록대장_2024!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">징계기록대장_2025!$1:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2026년'!$A$7:$J$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2018년'!$A$1:$K$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2019년'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2020년'!$A$1:$K$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'2021년'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'2022년'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2023년'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'2024년'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'2025년'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'2026년'!$A$1:$J$125</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2018년'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2019년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2020년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'2021년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'2022년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2023년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2024년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'2025년'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'2026년'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4226,6 +4226,30 @@
     <xf numFmtId="14" fontId="11" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4264,30 +4288,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="5" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5396,19 +5396,19 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="26.25">
-      <c r="A3" s="156" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
+      <c r="A3" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -5417,48 +5417,48 @@
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="152" t="s">
+      <c r="F5" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="163"/>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="158"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
+      <c r="A6" s="166"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
       <c r="J6" s="3" t="s">
         <v>11</v>
       </c>
@@ -5980,19 +5980,19 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="26.25">
-      <c r="A3" s="156" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
+      <c r="A3" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -6001,48 +6001,48 @@
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="152" t="s">
+      <c r="F5" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="163"/>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="158"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
+      <c r="A6" s="166"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
       <c r="J6" s="3" t="s">
         <v>11</v>
       </c>
@@ -6920,19 +6920,19 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="26.25">
-      <c r="A3" s="156" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
+      <c r="A3" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -6941,48 +6941,48 @@
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="152" t="s">
+      <c r="F5" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="163"/>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="158"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
+      <c r="A6" s="166"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
       <c r="J6" s="3" t="s">
         <v>11</v>
       </c>
@@ -7756,19 +7756,19 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="26.25">
-      <c r="A3" s="156" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
+      <c r="A3" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -7777,48 +7777,48 @@
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="152" t="s">
+      <c r="F5" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="163"/>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="158"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
+      <c r="A6" s="166"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
       <c r="J6" s="3" t="s">
         <v>11</v>
       </c>
@@ -8718,19 +8718,19 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="26.25">
-      <c r="A3" s="156" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
+      <c r="A3" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -8739,48 +8739,48 @@
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="152" t="s">
+      <c r="F5" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="152" t="s">
+      <c r="I5" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="163"/>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="158"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
+      <c r="A6" s="166"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
       <c r="J6" s="3" t="s">
         <v>11</v>
       </c>
@@ -9117,18 +9117,18 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="26.25">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="164" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -9138,48 +9138,48 @@
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="163" t="s">
+      <c r="B5" s="171" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="163" t="s">
+      <c r="C5" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="163" t="s">
+      <c r="D5" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="163" t="s">
+      <c r="E5" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="163" t="s">
+      <c r="H5" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="163" t="s">
+      <c r="I5" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="159" t="s">
+      <c r="J5" s="167" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="162"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="160"/>
+      <c r="A6" s="170"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="168"/>
     </row>
     <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1">
       <c r="A7" s="50">
@@ -9676,18 +9676,18 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="26.25">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="164" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -9697,48 +9697,48 @@
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="163" t="s">
+      <c r="B5" s="171" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="163" t="s">
+      <c r="C5" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="163" t="s">
+      <c r="D5" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="163" t="s">
+      <c r="E5" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="163" t="s">
+      <c r="H5" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="163" t="s">
+      <c r="I5" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="159" t="s">
+      <c r="J5" s="167" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="162"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="160"/>
+      <c r="A6" s="170"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="168"/>
     </row>
     <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1">
       <c r="A7" s="61">
@@ -10584,18 +10584,18 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="26.25">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="164" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -10605,48 +10605,48 @@
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="163" t="s">
+      <c r="B5" s="171" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="163" t="s">
+      <c r="C5" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="163" t="s">
+      <c r="D5" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="163" t="s">
+      <c r="E5" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="163" t="s">
+      <c r="H5" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="163" t="s">
+      <c r="I5" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="159" t="s">
+      <c r="J5" s="167" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="162"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="160"/>
+      <c r="A6" s="170"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="168"/>
     </row>
     <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1">
       <c r="A7" s="61">
@@ -11367,18 +11367,18 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:21" ht="26.25">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="164" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:21" ht="17.25" thickBot="1">
       <c r="A4" s="22" t="s">
@@ -11388,34 +11388,34 @@
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:21" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="163" t="s">
+      <c r="B5" s="171" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="163" t="s">
+      <c r="C5" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="163" t="s">
+      <c r="D5" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="163" t="s">
+      <c r="E5" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="163" t="s">
+      <c r="H5" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="163" t="s">
+      <c r="I5" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="159" t="s">
+      <c r="J5" s="167" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="135" t="s">
@@ -11450,16 +11450,16 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="162"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="160"/>
+      <c r="A6" s="170"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="168"/>
       <c r="L6" s="135">
         <f>SUMIF($I$8:$I$206,"훈계*",$K$8:$K$206)</f>
         <v>1</v>
@@ -18148,65 +18148,65 @@
       </c>
     </row>
     <row r="196" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A196" s="165">
+      <c r="A196" s="152">
         <f t="shared" si="2"/>
         <v>189</v>
       </c>
-      <c r="B196" s="166">
+      <c r="B196" s="153">
         <v>2026</v>
       </c>
-      <c r="C196" s="167"/>
-      <c r="D196" s="168">
+      <c r="C196" s="154"/>
+      <c r="D196" s="155">
         <v>46142</v>
       </c>
-      <c r="E196" s="169" t="s">
+      <c r="E196" s="156" t="s">
         <v>568</v>
       </c>
-      <c r="F196" s="169" t="s">
+      <c r="F196" s="156" t="s">
         <v>28</v>
       </c>
-      <c r="G196" s="169" t="s">
+      <c r="G196" s="156" t="s">
         <v>569</v>
       </c>
-      <c r="H196" s="170" t="s">
+      <c r="H196" s="157" t="s">
         <v>578</v>
       </c>
-      <c r="I196" s="169" t="s">
+      <c r="I196" s="156" t="s">
         <v>494</v>
       </c>
-      <c r="J196" s="171"/>
-      <c r="K196" s="172"/>
+      <c r="J196" s="158"/>
+      <c r="K196" s="159"/>
       <c r="N196" s="134"/>
     </row>
     <row r="197" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A197" s="165">
+      <c r="A197" s="152">
         <f t="shared" si="2"/>
         <v>190</v>
       </c>
-      <c r="B197" s="166">
+      <c r="B197" s="153">
         <v>2026</v>
       </c>
-      <c r="C197" s="167"/>
-      <c r="D197" s="168">
+      <c r="C197" s="154"/>
+      <c r="D197" s="155">
         <v>46142</v>
       </c>
-      <c r="E197" s="169" t="s">
+      <c r="E197" s="156" t="s">
         <v>537</v>
       </c>
-      <c r="F197" s="169" t="s">
+      <c r="F197" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="G197" s="169" t="s">
+      <c r="G197" s="156" t="s">
         <v>538</v>
       </c>
-      <c r="H197" s="170" t="s">
+      <c r="H197" s="157" t="s">
         <v>578</v>
       </c>
-      <c r="I197" s="169" t="s">
+      <c r="I197" s="156" t="s">
         <v>494</v>
       </c>
-      <c r="J197" s="171"/>
-      <c r="K197" s="172"/>
+      <c r="J197" s="158"/>
+      <c r="K197" s="159"/>
     </row>
     <row r="198" spans="1:14" ht="24.95" customHeight="1">
       <c r="A198" s="111">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ys.chun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6827C1-6348-4C13-AAAF-3081C83F4846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAD52FC-64D3-4030-AFE0-6B038547D706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="509">
   <si>
     <r>
       <t>[</t>
@@ -2239,12 +2239,29 @@
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>서울드래곤시티</t>
+  </si>
+  <si>
+    <t>소장</t>
+  </si>
+  <si>
+    <t>이상환</t>
+  </si>
+  <si>
+    <t>복무규정위반(객실 오출입)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>허중만</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4617,7 +4634,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:K23"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" customWidth="1"/>
@@ -4631,13 +4648,13 @@
     <col min="10" max="11" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="26.25">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>1</v>
       </c>
@@ -4652,13 +4669,13 @@
       <c r="J3" s="127"/>
       <c r="K3" s="127"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" thickBot="1">
+    <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="128" t="s">
         <v>2</v>
       </c>
@@ -4691,7 +4708,7 @@
       </c>
       <c r="K5" s="126"/>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="129"/>
       <c r="B6" s="124"/>
       <c r="C6" s="124"/>
@@ -4708,7 +4725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -4739,7 +4756,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1">
+    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2</v>
       </c>
@@ -4770,7 +4787,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1">
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
@@ -4801,7 +4818,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="21.95" customHeight="1">
+    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>4</v>
       </c>
@@ -4832,7 +4849,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1">
+    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
@@ -4863,7 +4880,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1">
+    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>6</v>
       </c>
@@ -4894,7 +4911,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" ht="21.95" customHeight="1">
+    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -4925,7 +4942,7 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1">
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -4956,7 +4973,7 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1">
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -4987,7 +5004,7 @@
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1">
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>10</v>
       </c>
@@ -5018,7 +5035,7 @@
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" ht="21.95" customHeight="1">
+    <row r="17" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>11</v>
       </c>
@@ -5049,7 +5066,7 @@
       <c r="J17" s="10"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" ht="21.95" customHeight="1">
+    <row r="18" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>12</v>
       </c>
@@ -5080,7 +5097,7 @@
       <c r="J18" s="10"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" ht="21.95" customHeight="1">
+    <row r="19" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>13</v>
       </c>
@@ -5111,7 +5128,7 @@
       <c r="J19" s="10"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" ht="21.95" customHeight="1">
+    <row r="20" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>14</v>
       </c>
@@ -5142,7 +5159,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" ht="21.95" customHeight="1">
+    <row r="21" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -5157,7 +5174,7 @@
       <c r="J21" s="10"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="22" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
         <v>16</v>
       </c>
@@ -5172,7 +5189,7 @@
       <c r="J22" s="14"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:11" ht="17.25" thickTop="1"/>
+    <row r="23" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="H5:H6"/>
@@ -5201,7 +5218,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:K29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" customWidth="1"/>
@@ -5215,13 +5232,13 @@
     <col min="10" max="11" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="26.25">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>1</v>
       </c>
@@ -5236,13 +5253,13 @@
       <c r="J3" s="127"/>
       <c r="K3" s="127"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" thickBot="1">
+    <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>61</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="128" t="s">
         <v>2</v>
       </c>
@@ -5275,7 +5292,7 @@
       </c>
       <c r="K5" s="126"/>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="129"/>
       <c r="B6" s="124"/>
       <c r="C6" s="124"/>
@@ -5292,7 +5309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -5323,7 +5340,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1">
+    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2</v>
       </c>
@@ -5354,7 +5371,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1">
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
@@ -5385,7 +5402,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="21.95" customHeight="1">
+    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>4</v>
       </c>
@@ -5416,7 +5433,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1">
+    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
@@ -5447,7 +5464,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1">
+    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>6</v>
       </c>
@@ -5478,7 +5495,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" ht="21.95" customHeight="1">
+    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -5509,7 +5526,7 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1">
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -5540,7 +5557,7 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1">
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -5571,7 +5588,7 @@
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1">
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>10</v>
       </c>
@@ -5602,7 +5619,7 @@
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" ht="21.95" customHeight="1">
+    <row r="17" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>11</v>
       </c>
@@ -5633,7 +5650,7 @@
       <c r="J17" s="10"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" ht="21.95" customHeight="1">
+    <row r="18" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>12</v>
       </c>
@@ -5664,7 +5681,7 @@
       <c r="J18" s="10"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" ht="21.95" customHeight="1">
+    <row r="19" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>13</v>
       </c>
@@ -5695,7 +5712,7 @@
       <c r="J19" s="10"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" ht="21.95" customHeight="1">
+    <row r="20" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>14</v>
       </c>
@@ -5726,7 +5743,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" ht="21.95" customHeight="1">
+    <row r="21" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -5757,7 +5774,7 @@
       <c r="J21" s="10"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="21.95" customHeight="1">
+    <row r="22" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27">
         <v>16</v>
       </c>
@@ -5788,7 +5805,7 @@
       <c r="J22" s="29"/>
       <c r="K22" s="31"/>
     </row>
-    <row r="23" spans="1:11" ht="21.95" customHeight="1">
+    <row r="23" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27">
         <v>17</v>
       </c>
@@ -5819,7 +5836,7 @@
       <c r="J23" s="29"/>
       <c r="K23" s="31"/>
     </row>
-    <row r="24" spans="1:11" ht="21.95" customHeight="1">
+    <row r="24" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27">
         <v>18</v>
       </c>
@@ -5850,7 +5867,7 @@
       <c r="J24" s="29"/>
       <c r="K24" s="31"/>
     </row>
-    <row r="25" spans="1:11" ht="21.95" customHeight="1">
+    <row r="25" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
         <v>19</v>
       </c>
@@ -5881,7 +5898,7 @@
       <c r="J25" s="29"/>
       <c r="K25" s="31"/>
     </row>
-    <row r="26" spans="1:11" ht="21.95" customHeight="1">
+    <row r="26" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
         <v>20</v>
       </c>
@@ -5912,7 +5929,7 @@
       <c r="J26" s="29"/>
       <c r="K26" s="31"/>
     </row>
-    <row r="27" spans="1:11" ht="21.95" customHeight="1">
+    <row r="27" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>21</v>
       </c>
@@ -5943,7 +5960,7 @@
       <c r="J27" s="29"/>
       <c r="K27" s="31"/>
     </row>
-    <row r="28" spans="1:11" ht="21.95" customHeight="1">
+    <row r="28" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
         <v>22</v>
       </c>
@@ -5974,7 +5991,7 @@
       <c r="J28" s="29"/>
       <c r="K28" s="31"/>
     </row>
-    <row r="29" spans="1:11" ht="21.95" customHeight="1">
+    <row r="29" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="27">
         <v>23</v>
       </c>
@@ -6036,7 +6053,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:K30"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" customWidth="1"/>
@@ -6050,13 +6067,13 @@
     <col min="10" max="11" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="26.25">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>1</v>
       </c>
@@ -6071,13 +6088,13 @@
       <c r="J3" s="127"/>
       <c r="K3" s="127"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" thickBot="1">
+    <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>136</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="128" t="s">
         <v>2</v>
       </c>
@@ -6110,7 +6127,7 @@
       </c>
       <c r="K5" s="126"/>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="129"/>
       <c r="B6" s="124"/>
       <c r="C6" s="124"/>
@@ -6127,7 +6144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -6158,7 +6175,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1">
+    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2</v>
       </c>
@@ -6189,7 +6206,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1">
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
@@ -6220,7 +6237,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="21.95" customHeight="1">
+    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>4</v>
       </c>
@@ -6251,7 +6268,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1">
+    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
@@ -6282,7 +6299,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1">
+    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>6</v>
       </c>
@@ -6313,7 +6330,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" ht="21.95" customHeight="1">
+    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -6344,7 +6361,7 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1">
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -6375,7 +6392,7 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1">
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -6406,7 +6423,7 @@
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1">
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>10</v>
       </c>
@@ -6437,7 +6454,7 @@
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" ht="21.95" customHeight="1">
+    <row r="17" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>11</v>
       </c>
@@ -6468,7 +6485,7 @@
       <c r="J17" s="10"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" ht="21.95" customHeight="1">
+    <row r="18" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>12</v>
       </c>
@@ -6499,7 +6516,7 @@
       <c r="J18" s="10"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" ht="21.95" customHeight="1">
+    <row r="19" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>13</v>
       </c>
@@ -6530,7 +6547,7 @@
       <c r="J19" s="10"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" ht="21.95" customHeight="1">
+    <row r="20" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>14</v>
       </c>
@@ -6561,7 +6578,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" ht="21.95" customHeight="1">
+    <row r="21" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -6592,7 +6609,7 @@
       <c r="J21" s="10"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="21.95" customHeight="1">
+    <row r="22" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27">
         <v>16</v>
       </c>
@@ -6623,7 +6640,7 @@
       <c r="J22" s="29"/>
       <c r="K22" s="31"/>
     </row>
-    <row r="23" spans="1:11" ht="21.95" customHeight="1">
+    <row r="23" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27">
         <v>17</v>
       </c>
@@ -6654,7 +6671,7 @@
       <c r="J23" s="29"/>
       <c r="K23" s="31"/>
     </row>
-    <row r="24" spans="1:11" ht="21.95" customHeight="1">
+    <row r="24" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27">
         <v>18</v>
       </c>
@@ -6685,7 +6702,7 @@
       <c r="J24" s="29"/>
       <c r="K24" s="31"/>
     </row>
-    <row r="25" spans="1:11" ht="21.95" customHeight="1">
+    <row r="25" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
         <v>19</v>
       </c>
@@ -6716,7 +6733,7 @@
       <c r="J25" s="29"/>
       <c r="K25" s="31"/>
     </row>
-    <row r="26" spans="1:11" ht="21.95" customHeight="1">
+    <row r="26" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
         <v>20</v>
       </c>
@@ -6747,7 +6764,7 @@
       <c r="J26" s="29"/>
       <c r="K26" s="31"/>
     </row>
-    <row r="27" spans="1:11" ht="21.95" customHeight="1">
+    <row r="27" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>21</v>
       </c>
@@ -6778,7 +6795,7 @@
       <c r="J27" s="29"/>
       <c r="K27" s="31"/>
     </row>
-    <row r="28" spans="1:11" ht="21.95" customHeight="1">
+    <row r="28" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
         <v>22</v>
       </c>
@@ -6809,7 +6826,7 @@
       <c r="J28" s="29"/>
       <c r="K28" s="31"/>
     </row>
-    <row r="29" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="29" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="108">
         <v>23</v>
       </c>
@@ -6840,7 +6857,7 @@
       <c r="J29" s="111"/>
       <c r="K29" s="113"/>
     </row>
-    <row r="30" spans="1:11" ht="17.25" thickTop="1"/>
+    <row r="30" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="J5:K5"/>
@@ -6872,7 +6889,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:K36"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" customWidth="1"/>
@@ -6886,13 +6903,13 @@
     <col min="10" max="11" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="26.25">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>1</v>
       </c>
@@ -6907,13 +6924,13 @@
       <c r="J3" s="127"/>
       <c r="K3" s="127"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" thickBot="1">
+    <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>213</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="128" t="s">
         <v>2</v>
       </c>
@@ -6946,7 +6963,7 @@
       </c>
       <c r="K5" s="126"/>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="129"/>
       <c r="B6" s="124"/>
       <c r="C6" s="124"/>
@@ -6963,7 +6980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -6994,7 +7011,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="24.95" customHeight="1">
+    <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2</v>
       </c>
@@ -7025,7 +7042,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="24.95" customHeight="1">
+    <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
@@ -7054,7 +7071,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="24.95" customHeight="1">
+    <row r="10" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>4</v>
       </c>
@@ -7085,7 +7102,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" ht="24.95" customHeight="1">
+    <row r="11" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
@@ -7114,7 +7131,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="24.95" customHeight="1">
+    <row r="12" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>6</v>
       </c>
@@ -7145,7 +7162,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" ht="24.95" customHeight="1">
+    <row r="13" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -7174,7 +7191,7 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="24.95" customHeight="1">
+    <row r="14" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -7205,7 +7222,7 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" ht="24.95" customHeight="1">
+    <row r="15" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -7232,7 +7249,7 @@
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" ht="24.95" customHeight="1">
+    <row r="16" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>10</v>
       </c>
@@ -7263,7 +7280,7 @@
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" ht="24.95" customHeight="1">
+    <row r="17" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>11</v>
       </c>
@@ -7294,7 +7311,7 @@
       <c r="J17" s="10"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" ht="24.95" customHeight="1">
+    <row r="18" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>12</v>
       </c>
@@ -7323,7 +7340,7 @@
       <c r="J18" s="10"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" ht="24.95" customHeight="1">
+    <row r="19" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>13</v>
       </c>
@@ -7352,7 +7369,7 @@
       <c r="J19" s="10"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" ht="24.95" customHeight="1">
+    <row r="20" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>14</v>
       </c>
@@ -7383,7 +7400,7 @@
       <c r="J20" s="10"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" ht="24.95" customHeight="1">
+    <row r="21" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -7412,7 +7429,7 @@
       <c r="J21" s="10"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="24.95" customHeight="1">
+    <row r="22" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27">
         <v>16</v>
       </c>
@@ -7443,7 +7460,7 @@
       <c r="J22" s="29"/>
       <c r="K22" s="31"/>
     </row>
-    <row r="23" spans="1:11" ht="24.95" customHeight="1">
+    <row r="23" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27">
         <v>17</v>
       </c>
@@ -7472,7 +7489,7 @@
       <c r="J23" s="29"/>
       <c r="K23" s="31"/>
     </row>
-    <row r="24" spans="1:11" ht="24.95" customHeight="1">
+    <row r="24" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27">
         <v>18</v>
       </c>
@@ -7501,7 +7518,7 @@
       <c r="J24" s="29"/>
       <c r="K24" s="31"/>
     </row>
-    <row r="25" spans="1:11" ht="24.95" customHeight="1">
+    <row r="25" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
         <v>19</v>
       </c>
@@ -7532,7 +7549,7 @@
       <c r="J25" s="29"/>
       <c r="K25" s="31"/>
     </row>
-    <row r="26" spans="1:11" ht="24.95" customHeight="1">
+    <row r="26" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
         <v>20</v>
       </c>
@@ -7561,7 +7578,7 @@
       <c r="J26" s="29"/>
       <c r="K26" s="31"/>
     </row>
-    <row r="27" spans="1:11" ht="24.95" customHeight="1">
+    <row r="27" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>21</v>
       </c>
@@ -7592,7 +7609,7 @@
       <c r="J27" s="29"/>
       <c r="K27" s="31"/>
     </row>
-    <row r="28" spans="1:11" ht="24.95" customHeight="1">
+    <row r="28" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
         <v>22</v>
       </c>
@@ -7623,7 +7640,7 @@
       <c r="J28" s="29"/>
       <c r="K28" s="31"/>
     </row>
-    <row r="29" spans="1:11" ht="24.95" customHeight="1">
+    <row r="29" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="27">
         <v>23</v>
       </c>
@@ -7650,7 +7667,7 @@
       <c r="J29" s="29"/>
       <c r="K29" s="31"/>
     </row>
-    <row r="30" spans="1:11" ht="24.95" customHeight="1">
+    <row r="30" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27">
         <v>24</v>
       </c>
@@ -7675,7 +7692,7 @@
       <c r="J30" s="29"/>
       <c r="K30" s="31"/>
     </row>
-    <row r="31" spans="1:11" ht="24.95" customHeight="1">
+    <row r="31" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="27">
         <v>25</v>
       </c>
@@ -7700,7 +7717,7 @@
       <c r="J31" s="29"/>
       <c r="K31" s="31"/>
     </row>
-    <row r="32" spans="1:11" ht="24.95" customHeight="1">
+    <row r="32" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="27">
         <v>26</v>
       </c>
@@ -7725,7 +7742,7 @@
       <c r="J32" s="29"/>
       <c r="K32" s="31"/>
     </row>
-    <row r="33" spans="1:11" ht="24.95" customHeight="1">
+    <row r="33" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="27">
         <v>27</v>
       </c>
@@ -7750,7 +7767,7 @@
       <c r="J33" s="29"/>
       <c r="K33" s="31"/>
     </row>
-    <row r="34" spans="1:11" ht="24.95" customHeight="1">
+    <row r="34" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="27">
         <v>28</v>
       </c>
@@ -7775,7 +7792,7 @@
       <c r="J34" s="29"/>
       <c r="K34" s="31"/>
     </row>
-    <row r="35" spans="1:11" ht="24.95" customHeight="1" thickBot="1">
+    <row r="35" spans="1:11" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="108">
         <v>29</v>
       </c>
@@ -7802,7 +7819,7 @@
       <c r="J35" s="111"/>
       <c r="K35" s="113"/>
     </row>
-    <row r="36" spans="1:11" ht="17.25" thickTop="1"/>
+    <row r="36" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="J5:K5"/>
@@ -7834,7 +7851,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:K16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="6.625" customWidth="1"/>
@@ -7848,13 +7865,13 @@
     <col min="10" max="11" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="26.25">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>1</v>
       </c>
@@ -7869,13 +7886,13 @@
       <c r="J3" s="127"/>
       <c r="K3" s="127"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" thickBot="1">
+    <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>318</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="128" t="s">
         <v>2</v>
       </c>
@@ -7908,7 +7925,7 @@
       </c>
       <c r="K5" s="126"/>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="129"/>
       <c r="B6" s="124"/>
       <c r="C6" s="124"/>
@@ -7925,7 +7942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -7956,7 +7973,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="24.95" customHeight="1">
+    <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2</v>
       </c>
@@ -7987,7 +8004,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="24.95" customHeight="1">
+    <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
@@ -8018,7 +8035,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="24.95" customHeight="1">
+    <row r="10" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>4</v>
       </c>
@@ -8049,7 +8066,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" ht="24.95" customHeight="1">
+    <row r="11" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
@@ -8080,7 +8097,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="24.95" customHeight="1">
+    <row r="12" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>6</v>
       </c>
@@ -8111,7 +8128,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" ht="24.95" customHeight="1">
+    <row r="13" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -8142,7 +8159,7 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="24.95" customHeight="1">
+    <row r="14" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -8173,7 +8190,7 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" ht="24.95" customHeight="1" thickBot="1">
+    <row r="15" spans="1:11" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="108">
         <v>9</v>
       </c>
@@ -8204,7 +8221,7 @@
       <c r="J15" s="111"/>
       <c r="K15" s="113"/>
     </row>
-    <row r="16" spans="1:11" ht="17.25" thickTop="1"/>
+    <row r="16" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="J5:K5"/>
@@ -8233,7 +8250,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B519C73E-B434-4010-BF9C-BCD0188C14F1}">
   <dimension ref="A2:J20"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.625" customWidth="1"/>
     <col min="3" max="3" width="6.625" customWidth="1"/>
@@ -8246,14 +8263,14 @@
     <col min="10" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="26.25">
+    <row r="3" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>210</v>
       </c>
@@ -8267,14 +8284,14 @@
       <c r="I3" s="127"/>
       <c r="J3" s="127"/>
     </row>
-    <row r="4" spans="1:10" ht="17.25" thickBot="1">
+    <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>501</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="21.95" customHeight="1">
+    <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
         <v>2</v>
       </c>
@@ -8306,7 +8323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="133"/>
       <c r="B6" s="135"/>
       <c r="C6" s="135"/>
@@ -8318,7 +8335,7 @@
       <c r="I6" s="135"/>
       <c r="J6" s="131"/>
     </row>
-    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="42">
         <f>ROW()-6</f>
         <v>1</v>
@@ -8351,7 +8368,7 @@
         <v>44993</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="24.95" customHeight="1">
+    <row r="8" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <f t="shared" ref="A8:A20" si="0">ROW()-6</f>
         <v>2</v>
@@ -8380,7 +8397,7 @@
         <v>44993</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="24.95" customHeight="1">
+    <row r="9" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -8413,7 +8430,7 @@
         <v>45006</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="96" customFormat="1" ht="24.95" customHeight="1">
+    <row r="10" spans="1:10" s="96" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="74">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -8446,7 +8463,7 @@
         <v>45022</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="24.95" customHeight="1">
+    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -8473,7 +8490,7 @@
       </c>
       <c r="J11" s="54"/>
     </row>
-    <row r="12" spans="1:10" ht="24.95" customHeight="1">
+    <row r="12" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -8500,7 +8517,7 @@
       </c>
       <c r="J12" s="54"/>
     </row>
-    <row r="13" spans="1:10" ht="24.95" customHeight="1">
+    <row r="13" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -8533,7 +8550,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="24.95" customHeight="1">
+    <row r="14" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -8566,7 +8583,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24.95" customHeight="1">
+    <row r="15" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -8599,7 +8616,7 @@
         <v>45112</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="24.95" customHeight="1">
+    <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -8632,7 +8649,7 @@
         <v>45182</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="24.95" customHeight="1">
+    <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -8665,7 +8682,7 @@
         <v>45182</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1">
+    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8698,7 +8715,7 @@
         <v>45182</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1">
+    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -8731,7 +8748,7 @@
         <v>45183</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1" thickBot="1">
+    <row r="20" spans="1:10" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="40">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -8792,7 +8809,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE09A89-A226-4252-9463-FC92CB461B84}">
   <dimension ref="A2:J31"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.625" customWidth="1"/>
     <col min="3" max="3" width="6.625" customWidth="1"/>
@@ -8805,14 +8822,14 @@
     <col min="10" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="26.25">
+    <row r="3" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>210</v>
       </c>
@@ -8826,14 +8843,14 @@
       <c r="I3" s="127"/>
       <c r="J3" s="127"/>
     </row>
-    <row r="4" spans="1:10" ht="17.25" thickBot="1">
+    <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>502</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="21.95" customHeight="1">
+    <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
         <v>2</v>
       </c>
@@ -8865,7 +8882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="133"/>
       <c r="B6" s="135"/>
       <c r="C6" s="135"/>
@@ -8877,7 +8894,7 @@
       <c r="I6" s="135"/>
       <c r="J6" s="131"/>
     </row>
-    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <f>ROW()-6</f>
         <v>1</v>
@@ -8910,7 +8927,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="24.95" customHeight="1">
+    <row r="8" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <f t="shared" ref="A8:A31" si="0">ROW()-6</f>
         <v>2</v>
@@ -8943,7 +8960,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="24.95" customHeight="1">
+    <row r="9" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -8976,7 +8993,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="24.95" customHeight="1">
+    <row r="10" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9009,7 +9026,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="24.95" customHeight="1">
+    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9042,7 +9059,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="24.95" customHeight="1">
+    <row r="12" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9075,7 +9092,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="24.95" customHeight="1">
+    <row r="13" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9108,7 +9125,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="24.95" customHeight="1">
+    <row r="14" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9141,7 +9158,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24.95" customHeight="1">
+    <row r="15" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9170,7 +9187,7 @@
         <v>45532</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="24.95" customHeight="1">
+    <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9203,7 +9220,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="24.95" customHeight="1">
+    <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9236,7 +9253,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1">
+    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9269,7 +9286,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1">
+    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -9300,7 +9317,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1">
+    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -9331,7 +9348,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="24.95" customHeight="1">
+    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -9362,7 +9379,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="24.95" customHeight="1">
+    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -9393,7 +9410,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="24.95" customHeight="1">
+    <row r="23" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -9424,7 +9441,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="24.95" customHeight="1">
+    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -9455,7 +9472,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="24.95" customHeight="1">
+    <row r="25" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -9486,7 +9503,7 @@
         <v>45593</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="24.95" customHeight="1">
+    <row r="26" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9517,7 +9534,7 @@
         <v>45593</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="24.95" customHeight="1">
+    <row r="27" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -9548,7 +9565,7 @@
         <v>45596</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="24.95" customHeight="1">
+    <row r="28" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9579,7 +9596,7 @@
         <v>45596</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="24.95" customHeight="1">
+    <row r="29" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -9610,7 +9627,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="24.95" customHeight="1">
+    <row r="30" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -9641,7 +9658,7 @@
         <v>45638</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="24.95" customHeight="1" thickBot="1">
+    <row r="31" spans="1:10" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="40">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9700,7 +9717,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B5296A-BF2F-408D-8618-76F8BAA89476}">
   <dimension ref="A2:J27"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.625" customWidth="1"/>
     <col min="3" max="3" width="6.625" customWidth="1"/>
@@ -9713,14 +9730,14 @@
     <col min="10" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="26.25">
+    <row r="3" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>210</v>
       </c>
@@ -9734,14 +9751,14 @@
       <c r="I3" s="127"/>
       <c r="J3" s="127"/>
     </row>
-    <row r="4" spans="1:10" ht="17.25" thickBot="1">
+    <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>503</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="21.95" customHeight="1">
+    <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
         <v>2</v>
       </c>
@@ -9773,7 +9790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:10" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="133"/>
       <c r="B6" s="135"/>
       <c r="C6" s="135"/>
@@ -9785,7 +9802,7 @@
       <c r="I6" s="135"/>
       <c r="J6" s="131"/>
     </row>
-    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:10" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <f>ROW()-6</f>
         <v>1</v>
@@ -9816,7 +9833,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="24.95" customHeight="1">
+    <row r="8" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <f t="shared" ref="A8:A27" si="0">ROW()-6</f>
         <v>2</v>
@@ -9847,7 +9864,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="24.95" customHeight="1">
+    <row r="9" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -9878,7 +9895,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="24.95" customHeight="1">
+    <row r="10" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9909,7 +9926,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="24.95" customHeight="1">
+    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="89">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9942,7 +9959,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="24.95" customHeight="1">
+    <row r="12" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9975,7 +9992,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="24.95" customHeight="1">
+    <row r="13" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="89">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10008,7 +10025,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="24.95" customHeight="1">
+    <row r="14" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10039,7 +10056,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24.95" customHeight="1">
+    <row r="15" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10070,7 +10087,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="24.95" customHeight="1">
+    <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10101,7 +10118,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="24.95" customHeight="1">
+    <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="89">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10132,7 +10149,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1">
+    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10163,7 +10180,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1">
+    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10194,7 +10211,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1">
+    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="89">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10227,7 +10244,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="24.95" customHeight="1">
+    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="89">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10260,7 +10277,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="24.95" customHeight="1">
+    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="89">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10293,7 +10310,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="24.95" customHeight="1">
+    <row r="23" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="89">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10326,7 +10343,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="24.95" customHeight="1">
+    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -10357,7 +10374,7 @@
         <v>45867</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="24.95" customHeight="1">
+    <row r="25" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -10388,7 +10405,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="24.95" customHeight="1">
+    <row r="26" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -10419,7 +10436,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="114" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
+    <row r="27" spans="1:10" s="114" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="97">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -10483,7 +10500,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A2:U37"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.625" customWidth="1"/>
     <col min="3" max="3" width="6.625" customWidth="1"/>
@@ -10496,14 +10513,14 @@
     <col min="10" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="26.25">
+    <row r="3" spans="1:21" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="127" t="s">
         <v>210</v>
       </c>
@@ -10517,14 +10534,14 @@
       <c r="I3" s="127"/>
       <c r="J3" s="127"/>
     </row>
-    <row r="4" spans="1:21" ht="17.25" thickBot="1">
+    <row r="4" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>212</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="21.95" customHeight="1" thickBot="1">
+    <row r="5" spans="1:21" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="132" t="s">
         <v>2</v>
       </c>
@@ -10586,7 +10603,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="21.95" customHeight="1" thickBot="1">
+    <row r="6" spans="1:21" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="133"/>
       <c r="B6" s="135"/>
       <c r="C6" s="135"/>
@@ -10638,7 +10655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="21.95" customHeight="1" thickTop="1">
+    <row r="7" spans="1:21" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64"/>
       <c r="B7" s="65"/>
       <c r="C7" s="65"/>
@@ -10650,7 +10667,7 @@
       <c r="I7" s="65"/>
       <c r="J7" s="66"/>
     </row>
-    <row r="8" spans="1:21" ht="24.95" customHeight="1">
+    <row r="8" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="82">
         <f t="shared" ref="A8:A37" si="0">ROW()-7</f>
         <v>1</v>
@@ -10684,7 +10701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="24.95" customHeight="1">
+    <row r="9" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -10718,7 +10735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="24.95" customHeight="1">
+    <row r="10" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10752,7 +10769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="24.95" customHeight="1">
+    <row r="11" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="81">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10786,7 +10803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="24.95" customHeight="1">
+    <row r="12" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="89">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10820,7 +10837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="24.95" customHeight="1">
+    <row r="13" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10854,7 +10871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="24.95" customHeight="1">
+    <row r="14" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10888,7 +10905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="24.95" customHeight="1">
+    <row r="15" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10922,7 +10939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="24.95" customHeight="1">
+    <row r="16" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10956,7 +10973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="24.95" customHeight="1">
+    <row r="17" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10990,7 +11007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="24.95" customHeight="1">
+    <row r="18" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="89">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -11024,7 +11041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="24.95" customHeight="1">
+    <row r="19" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11058,7 +11075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="24.95" customHeight="1">
+    <row r="20" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11092,7 +11109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="24.95" customHeight="1">
+    <row r="21" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -11126,7 +11143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="24.95" customHeight="1">
+    <row r="22" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11160,7 +11177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="24.95" customHeight="1">
+    <row r="23" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="89">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -11196,7 +11213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="24.95" customHeight="1">
+    <row r="24" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11232,7 +11249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="24.95" customHeight="1">
+    <row r="25" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -11268,7 +11285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="24.95" customHeight="1">
+    <row r="26" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -11304,7 +11321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="24.95" customHeight="1">
+    <row r="27" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="115">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -11335,7 +11352,7 @@
       <c r="K27" s="122"/>
       <c r="N27" s="104"/>
     </row>
-    <row r="28" spans="1:14" ht="24.95" customHeight="1">
+    <row r="28" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="115">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -11365,7 +11382,7 @@
       <c r="J28" s="121"/>
       <c r="K28" s="122"/>
     </row>
-    <row r="29" spans="1:14" ht="24.95" customHeight="1">
+    <row r="29" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="81">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -11401,7 +11418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="24.95" customHeight="1">
+    <row r="30" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="81">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11437,7 +11454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="24.95" customHeight="1">
+    <row r="31" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="81">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11473,7 +11490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="24.95" customHeight="1">
+    <row r="32" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="81">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11509,7 +11526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="24.95" customHeight="1">
+    <row r="33" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="81">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -11545,37 +11562,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="24.95" customHeight="1">
+    <row r="34" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B34" s="69"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="73"/>
-    </row>
-    <row r="35" spans="1:11" ht="24.95" customHeight="1">
+      <c r="B34" s="69">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" s="68">
+        <v>46198</v>
+      </c>
+      <c r="E34" s="71" t="s">
+        <v>504</v>
+      </c>
+      <c r="F34" s="71" t="s">
+        <v>505</v>
+      </c>
+      <c r="G34" s="71" t="s">
+        <v>506</v>
+      </c>
+      <c r="H34" s="72" t="s">
+        <v>507</v>
+      </c>
+      <c r="I34" s="71" t="s">
+        <v>491</v>
+      </c>
+      <c r="J34" s="73">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B35" s="69"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="73"/>
-    </row>
-    <row r="36" spans="1:11" ht="24.95" customHeight="1">
+      <c r="B35" s="69">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="D35" s="68">
+        <v>46198</v>
+      </c>
+      <c r="E35" s="71" t="s">
+        <v>504</v>
+      </c>
+      <c r="F35" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="71" t="s">
+        <v>508</v>
+      </c>
+      <c r="H35" s="72" t="s">
+        <v>507</v>
+      </c>
+      <c r="I35" s="71" t="s">
+        <v>491</v>
+      </c>
+      <c r="J35" s="73">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -11590,7 +11643,7 @@
       <c r="I36" s="44"/>
       <c r="J36" s="62"/>
     </row>
-    <row r="37" spans="1:11" ht="24.95" customHeight="1" thickBot="1">
+    <row r="37" spans="1:11" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="40">
         <f t="shared" si="0"/>
         <v>30</v>
